--- a/data/trans_orig/Q17F_D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario</t>
+          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 19,17</t>
+          <t>6,79; 19,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 17,26</t>
+          <t>4,92; 17,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 17,74</t>
+          <t>4,82; 18,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,88; 37,03</t>
+          <t>17,94; 41,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 32,69</t>
+          <t>7,41; 33,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 14,26</t>
+          <t>3,47; 15,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 16,61</t>
+          <t>5,76; 14,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,81; 32,03</t>
+          <t>16,01; 32,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 21,17</t>
+          <t>8,79; 21,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 13,91</t>
+          <t>5,21; 13,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,12</t>
+          <t>5,96; 13,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 32,0</t>
+          <t>18,41; 32,47</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,26</t>
+          <t>4,21; 15,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 12,26</t>
+          <t>2,9; 11,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 20,6</t>
+          <t>4,23; 20,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 41,13</t>
+          <t>15,3; 42,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,94</t>
+          <t>4,39; 11,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 22,26</t>
+          <t>4,75; 23,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 64,25</t>
+          <t>11,87; 67,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 18,63</t>
+          <t>9,68; 19,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 10,54</t>
+          <t>4,98; 10,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 14,45</t>
+          <t>4,9; 16,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 34,08</t>
+          <t>9,58; 36,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,76; 27,79</t>
+          <t>13,68; 28,17</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 13,54</t>
+          <t>6,13; 13,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 22,16</t>
+          <t>10,33; 22,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,22</t>
+          <t>4,28; 13,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 34,31</t>
+          <t>10,49; 34,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 16,83</t>
+          <t>4,11; 15,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,96</t>
+          <t>4,16; 13,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 23,64</t>
+          <t>6,07; 23,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 61,05</t>
+          <t>12,51; 55,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,97</t>
+          <t>6,01; 12,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 16,9</t>
+          <t>8,55; 17,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,12</t>
+          <t>5,49; 13,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,01; 36,62</t>
+          <t>14,25; 34,69</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,0</t>
+          <t>7,36; 14,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,51</t>
+          <t>7,42; 14,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 17,3</t>
+          <t>8,65; 17,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 25,1</t>
+          <t>13,47; 24,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 18,71</t>
+          <t>7,54; 18,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 14,9</t>
+          <t>6,73; 14,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 31,94</t>
+          <t>10,1; 31,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,5; 31,61</t>
+          <t>16,84; 30,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 14,96</t>
+          <t>8,14; 14,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 13,57</t>
+          <t>7,89; 13,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 22,51</t>
+          <t>10,84; 22,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 25,06</t>
+          <t>16,41; 24,89</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 50,85</t>
+          <t>6,38; 57,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,79</t>
+          <t>3,96; 10,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 20,51</t>
+          <t>7,64; 19,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,81; 90,8</t>
+          <t>18,38; 88,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 15,38</t>
+          <t>6,06; 15,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 14,73</t>
+          <t>6,36; 15,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 20,2</t>
+          <t>8,8; 19,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,69; 30,92</t>
+          <t>11,02; 31,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 20,53</t>
+          <t>7,47; 22,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,49</t>
+          <t>5,96; 13,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,63; 18,02</t>
+          <t>9,78; 17,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,16; 39,3</t>
+          <t>15,21; 39,22</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,53</t>
+          <t>1,88; 8,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 13,53</t>
+          <t>2,88; 14,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 11,59</t>
+          <t>2,38; 12,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 37,71</t>
+          <t>3,75; 38,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,07</t>
+          <t>5,43; 11,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 17,4</t>
+          <t>8,73; 17,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 15,61</t>
+          <t>7,92; 15,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,65; 28,13</t>
+          <t>15,39; 28,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,67</t>
+          <t>5,36; 10,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 16,17</t>
+          <t>8,28; 16,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,88; 14,73</t>
+          <t>7,93; 14,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,45; 27,24</t>
+          <t>14,48; 26,95</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,08</t>
+          <t>8,12; 14,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,12</t>
+          <t>8,28; 12,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,81</t>
+          <t>7,95; 12,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,91; 30,94</t>
+          <t>18,85; 31,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,44</t>
+          <t>7,36; 11,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 12,25</t>
+          <t>8,06; 12,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 17,86</t>
+          <t>11,0; 17,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 24,6</t>
+          <t>16,1; 24,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,31; 11,49</t>
+          <t>8,27; 11,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,79</t>
+          <t>8,67; 11,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,4; 14,95</t>
+          <t>10,22; 14,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,52; 25,36</t>
+          <t>18,68; 25,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q17F_D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,27</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,12</t>
+          <t>23,47</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,78</t>
+          <t>25,26</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 19,44</t>
+          <t>6,89; 20,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 17,64</t>
+          <t>4,92; 16,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 18,66</t>
+          <t>4,68; 15,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,94; 41,89</t>
+          <t>18,84; 41,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 33,58</t>
+          <t>7,58; 31,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 15,13</t>
+          <t>3,46; 18,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 14,84</t>
+          <t>5,93; 15,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,01; 32,42</t>
+          <t>16,79; 34,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 21,35</t>
+          <t>8,83; 21,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 13,41</t>
+          <t>5,0; 12,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,49</t>
+          <t>5,98; 13,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,41; 32,47</t>
+          <t>19,17; 33,67</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,11</t>
+          <t>24,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,04</t>
+          <t>12,66</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,12</t>
+          <t>18,46</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 15,2</t>
+          <t>4,03; 13,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,99</t>
+          <t>2,94; 11,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 20,03</t>
+          <t>4,15; 18,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,3; 42,56</t>
+          <t>15,79; 42,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,23</t>
+          <t>4,45; 11,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 23,42</t>
+          <t>5,09; 24,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,87; 67,45</t>
+          <t>12,06; 66,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 19,24</t>
+          <t>9,57; 18,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,47</t>
+          <t>4,96; 10,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,35</t>
+          <t>4,86; 15,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 36,26</t>
+          <t>9,64; 34,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 28,17</t>
+          <t>13,39; 27,35</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,04</t>
+          <t>17,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,91</t>
+          <t>28,53</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>21,74</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 13,81</t>
+          <t>6,06; 13,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 22,14</t>
+          <t>9,71; 21,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,01</t>
+          <t>4,09; 13,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,49; 34,38</t>
+          <t>9,65; 35,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 15,72</t>
+          <t>3,81; 15,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 13,23</t>
+          <t>3,89; 13,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 23,33</t>
+          <t>5,42; 24,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 55,73</t>
+          <t>14,74; 55,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 12,27</t>
+          <t>6,22; 12,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 17,17</t>
+          <t>8,62; 16,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 13,34</t>
+          <t>5,51; 12,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 34,69</t>
+          <t>14,27; 35,59</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,09</t>
+          <t>18,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,19</t>
+          <t>22,99</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,01</t>
+          <t>20,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 14,89</t>
+          <t>7,08; 15,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 14,93</t>
+          <t>7,88; 15,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 17,1</t>
+          <t>8,82; 17,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,47; 24,33</t>
+          <t>13,51; 24,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 18,9</t>
+          <t>7,07; 19,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 14,66</t>
+          <t>6,54; 15,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 31,93</t>
+          <t>9,74; 31,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 30,71</t>
+          <t>17,26; 30,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,35</t>
+          <t>8,04; 14,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 13,24</t>
+          <t>7,84; 13,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 22,51</t>
+          <t>10,5; 22,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,41; 24,89</t>
+          <t>16,39; 25,89</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40,72</t>
+          <t>39,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,71</t>
+          <t>27,55</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,69</t>
+          <t>31,13</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,38; 57,46</t>
+          <t>6,09; 53,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 10,65</t>
+          <t>3,9; 10,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 19,16</t>
+          <t>7,64; 19,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,38; 88,34</t>
+          <t>16,91; 84,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 15,77</t>
+          <t>5,93; 15,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,48</t>
+          <t>6,19; 15,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 19,31</t>
+          <t>9,06; 20,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,02; 31,71</t>
+          <t>20,3; 39,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 22,27</t>
+          <t>7,18; 20,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,27</t>
+          <t>5,86; 12,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,78; 17,84</t>
+          <t>9,38; 16,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,21; 39,22</t>
+          <t>22,77; 46,74</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>18,05</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,23</t>
+          <t>19,71</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,52</t>
+          <t>19,55</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,53</t>
+          <t>1,89; 8,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 14,95</t>
+          <t>2,48; 13,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 12,2</t>
+          <t>2,58; 12,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 38,36</t>
+          <t>5,65; 41,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,06</t>
+          <t>5,39; 11,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,73; 17,37</t>
+          <t>8,84; 17,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,92; 15,65</t>
+          <t>8,14; 15,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,39; 28,01</t>
+          <t>14,82; 27,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,82</t>
+          <t>5,41; 11,4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,28; 16,33</t>
+          <t>8,18; 16,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 14,63</t>
+          <t>7,76; 14,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,48; 26,95</t>
+          <t>14,68; 27,22</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,58</t>
+          <t>23,74</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,71</t>
+          <t>22,62</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,91</t>
+          <t>23,1</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,12; 14,25</t>
+          <t>8,12; 14,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,41</t>
+          <t>8,31; 12,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,46</t>
+          <t>7,91; 12,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,85; 31,01</t>
+          <t>19,06; 31,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,28</t>
+          <t>7,57; 11,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,33</t>
+          <t>8,23; 12,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,0; 17,77</t>
+          <t>11,21; 17,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,1; 24,79</t>
+          <t>19,73; 26,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,79</t>
+          <t>8,3; 11,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,47</t>
+          <t>8,61; 11,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,22; 14,51</t>
+          <t>10,5; 14,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,68; 25,49</t>
+          <t>20,31; 26,65</t>
         </is>
       </c>
     </row>
